--- a/AgentTb.xlsx
+++ b/AgentTb.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="AgentTb"/>
   </sheets>
   <definedNames>
-    <definedName name="AgentTb">'AgentTb'!$A$1:$X$1719</definedName>
+    <definedName name="AgentTb">'AgentTb'!$A$1:$X$1756</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X1719"/>
+  <dimension ref="A1:X1756"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -12748,31 +12748,26 @@
       </c>
       <c r="B250" s="0" t="inlineStr">
         <is>
-          <t>Debbie Andersen</t>
+          <t>Travis Pearce</t>
         </is>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
-          <t>SWBC Mortgage</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="J250" s="0" t="inlineStr">
         <is>
-          <t>8012944663</t>
-        </is>
-      </c>
-      <c r="L250" s="0" t="inlineStr">
-        <is>
-          <t>8012944662</t>
+          <t>8015806602</t>
         </is>
       </c>
       <c r="M250" s="0" t="inlineStr">
         <is>
-          <t>dandersen@swbc.com</t>
+          <t>tpearce@bhhsutah.com</t>
         </is>
       </c>
       <c r="S250" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T250" s="0" t="b">
         <v>0</v>
@@ -12781,10 +12776,10 @@
         <v>0</v>
       </c>
       <c r="V250" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W250" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X250" s="0" t="b">
         <v>0</v>
@@ -13652,37 +13647,32 @@
       </c>
       <c r="B268" s="0" t="inlineStr">
         <is>
-          <t>DeAnne Taylor</t>
+          <t>Lori Siekman</t>
         </is>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
-          <t>Monument Title</t>
+          <t>Inspire Home Loans</t>
         </is>
       </c>
       <c r="J268" s="0" t="inlineStr">
         <is>
-          <t>8016761076</t>
-        </is>
-      </c>
-      <c r="L268" s="0" t="inlineStr">
-        <is>
-          <t>8016761077</t>
+          <t>3034682336</t>
         </is>
       </c>
       <c r="M268" s="0" t="inlineStr">
         <is>
-          <t>dtaylor@monumenttitle.net</t>
+          <t>lori.siekman@inspirehomeloans.com</t>
         </is>
       </c>
       <c r="S268" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T268" s="0" t="b">
         <v>0</v>
       </c>
       <c r="U268" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V268" s="0" t="b">
         <v>0</v>
@@ -43496,7 +43486,7 @@
       </c>
       <c r="B884" s="0" t="inlineStr">
         <is>
-          <t>Debbie Bowden</t>
+          <t>Dav</t>
         </is>
       </c>
       <c r="C884" s="0" t="inlineStr">
@@ -44057,48 +44047,38 @@
       </c>
       <c r="B896" s="0" t="inlineStr">
         <is>
-          <t>Deann Taylor</t>
+          <t>Jesse Diaz</t>
         </is>
       </c>
       <c r="C896" s="0" t="inlineStr">
         <is>
-          <t>Monument Title</t>
+          <t>Century Communities</t>
         </is>
       </c>
       <c r="J896" s="0" t="inlineStr">
         <is>
-          <t>8016761076</t>
+          <t>8016691215</t>
         </is>
       </c>
       <c r="M896" s="0" t="inlineStr">
         <is>
-          <t>deann@monumenttitle.net</t>
-        </is>
-      </c>
-      <c r="N896" s="0" t="inlineStr">
-        <is>
-          <t>Jennifer</t>
-        </is>
-      </c>
-      <c r="R896" s="0" t="inlineStr">
-        <is>
-          <t>jennifer@monumenttitle.net</t>
+          <t>jesse.diaz@centurycommunities.com</t>
         </is>
       </c>
       <c r="S896" s="0" t="b">
         <v>0</v>
       </c>
       <c r="T896" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U896" s="0" t="b">
         <v>0</v>
       </c>
       <c r="V896" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W896" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X896" s="0" t="b">
         <v>0</v>
@@ -45159,37 +45139,22 @@
       </c>
       <c r="B920" s="0" t="inlineStr">
         <is>
-          <t>Dean Stokes</t>
+          <t>Erin Mehler</t>
         </is>
       </c>
       <c r="C920" s="0" t="inlineStr">
         <is>
-          <t>Century 21 Everest Group</t>
+          <t>EXP Realty</t>
         </is>
       </c>
       <c r="K920" s="0" t="inlineStr">
         <is>
-          <t>8014503907</t>
+          <t>8018889122</t>
         </is>
       </c>
       <c r="M920" s="0" t="inlineStr">
         <is>
-          <t>cdeanstokes@everestrealtygroup.com</t>
-        </is>
-      </c>
-      <c r="N920" s="0" t="inlineStr">
-        <is>
-          <t>Marshelle Clawson</t>
-        </is>
-      </c>
-      <c r="O920" s="0" t="inlineStr">
-        <is>
-          <t>8018712172</t>
-        </is>
-      </c>
-      <c r="R920" s="0" t="inlineStr">
-        <is>
-          <t>marshelle.clawson@century21everestrealty.com</t>
+          <t>erinmehler@gmail.com</t>
         </is>
       </c>
       <c r="S920" s="0" t="b">
@@ -45202,7 +45167,7 @@
         <v>0</v>
       </c>
       <c r="V920" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W920" s="0" t="b">
         <v>1</v>
@@ -45404,7 +45369,7 @@
       </c>
       <c r="C925" s="0" t="inlineStr">
         <is>
-          <t>Prime Residential Mortgage</t>
+          <t>Security National Mortgage</t>
         </is>
       </c>
       <c r="J925" s="0" t="inlineStr">
@@ -45414,7 +45379,7 @@
       </c>
       <c r="M925" s="0" t="inlineStr">
         <is>
-          <t>jdalton@primeres.com</t>
+          <t>jeff.dalton@snmc.com</t>
         </is>
       </c>
       <c r="S925" s="0" t="b">
@@ -80025,7 +79990,7 @@
       </c>
       <c r="B1705" s="0" t="inlineStr">
         <is>
-          <t>Dave Wright</t>
+          <t>Lesley Ulibarri</t>
         </is>
       </c>
       <c r="C1705" s="0" t="inlineStr">
@@ -80033,14 +79998,9 @@
           <t>Fidelity National Title</t>
         </is>
       </c>
-      <c r="K1705" s="0" t="inlineStr">
-        <is>
-          <t>8019159494</t>
-        </is>
-      </c>
       <c r="M1705" s="0" t="inlineStr">
         <is>
-          <t>UT.TeamDave@fnf.com</t>
+          <t>UT.Teamlesley@fnf.com</t>
         </is>
       </c>
       <c r="S1705" s="0" t="b">
@@ -80050,7 +80010,7 @@
         <v>1</v>
       </c>
       <c r="U1705" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1705" s="0" t="b">
         <v>0</v>
@@ -80326,31 +80286,26 @@
       </c>
       <c r="B1712" s="0" t="inlineStr">
         <is>
-          <t>Chris McPherson</t>
+          <t>Nichole Jones</t>
         </is>
       </c>
       <c r="C1712" s="0" t="inlineStr">
         <is>
-          <t>Guild Mortgage</t>
+          <t>Salt &amp; Summitt Real Estate Group</t>
         </is>
       </c>
       <c r="J1712" s="0" t="inlineStr">
         <is>
-          <t>8016760042</t>
-        </is>
-      </c>
-      <c r="K1712" s="0" t="inlineStr">
-        <is>
-          <t>8014555268</t>
+          <t>8017558721</t>
         </is>
       </c>
       <c r="M1712" s="0" t="inlineStr">
         <is>
-          <t>chris.macpherson@guildmortgage.net</t>
+          <t>nicholegetsgreen@gmail.com</t>
         </is>
       </c>
       <c r="S1712" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T1712" s="0" t="b">
         <v>0</v>
@@ -80359,10 +80314,10 @@
         <v>0</v>
       </c>
       <c r="V1712" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1712" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1712" s="0" t="b">
         <v>0</v>
@@ -80427,38 +80382,38 @@
       </c>
       <c r="B1714" s="0" t="inlineStr">
         <is>
-          <t>Dave Wright</t>
+          <t>Ethan Rowbury</t>
         </is>
       </c>
       <c r="C1714" s="0" t="inlineStr">
         <is>
-          <t>Fidelity National Title</t>
+          <t>R &amp; R Realty</t>
         </is>
       </c>
       <c r="K1714" s="0" t="inlineStr">
         <is>
-          <t>8019159494</t>
+          <t>3857754237</t>
         </is>
       </c>
       <c r="M1714" s="0" t="inlineStr">
         <is>
-          <t>UT.Teamdave@fnf.com</t>
+          <t>ethancrowbury@gmail.com</t>
         </is>
       </c>
       <c r="S1714" s="0" t="b">
         <v>0</v>
       </c>
       <c r="T1714" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U1714" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V1714" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W1714" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X1714" s="0" t="b">
         <v>0</v>
@@ -80528,22 +80483,17 @@
       </c>
       <c r="B1716" s="0" t="inlineStr">
         <is>
-          <t>Brandy Kramer</t>
+          <t>Steffanie Ferguson</t>
         </is>
       </c>
       <c r="C1716" s="0" t="inlineStr">
         <is>
-          <t>Meridian Title</t>
-        </is>
-      </c>
-      <c r="K1716" s="0" t="inlineStr">
-        <is>
-          <t>8012648888</t>
+          <t>Real Advantage Title</t>
         </is>
       </c>
       <c r="M1716" s="0" t="inlineStr">
         <is>
-          <t>brandyteam@mtcutah.com</t>
+          <t>steffteam@realadvantageutah.com</t>
         </is>
       </c>
       <c r="S1716" s="0" t="b">
@@ -80691,6 +80641,1637 @@
         <v>0</v>
       </c>
       <c r="X1719" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1720">
+      <c r="A1720" s="0">
+        <v>1721</v>
+      </c>
+      <c r="B1720" s="0" t="inlineStr">
+        <is>
+          <t>Ryan Almond</t>
+        </is>
+      </c>
+      <c r="C1720" s="0" t="inlineStr">
+        <is>
+          <t>Prime Lending</t>
+        </is>
+      </c>
+      <c r="J1720" s="0" t="inlineStr">
+        <is>
+          <t>8013182281</t>
+        </is>
+      </c>
+      <c r="M1720" s="0" t="inlineStr">
+        <is>
+          <t>ralmond@primelending.com</t>
+        </is>
+      </c>
+      <c r="S1720" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1720" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1720" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1720" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1720" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1720" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1721">
+      <c r="A1721" s="0">
+        <v>1722</v>
+      </c>
+      <c r="B1721" s="0" t="inlineStr">
+        <is>
+          <t>Hannah Curtis</t>
+        </is>
+      </c>
+      <c r="C1721" s="0" t="inlineStr">
+        <is>
+          <t>Equity Real Estate</t>
+        </is>
+      </c>
+      <c r="K1721" s="0" t="inlineStr">
+        <is>
+          <t>8018360082</t>
+        </is>
+      </c>
+      <c r="M1721" s="0" t="inlineStr">
+        <is>
+          <t>hannahcurtis615@gmail.com</t>
+        </is>
+      </c>
+      <c r="S1721" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1721" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1721" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1721" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="W1721" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1721" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1722">
+      <c r="A1722" s="0">
+        <v>1723</v>
+      </c>
+      <c r="B1722" s="0" t="inlineStr">
+        <is>
+          <t>Shawn Wolfley</t>
+        </is>
+      </c>
+      <c r="C1722" s="0" t="inlineStr">
+        <is>
+          <t>KW Unite Keller Williams</t>
+        </is>
+      </c>
+      <c r="K1722" s="0" t="inlineStr">
+        <is>
+          <t>4357602191</t>
+        </is>
+      </c>
+      <c r="M1722" s="0" t="inlineStr">
+        <is>
+          <t>shawnwolfley@gmail.com</t>
+        </is>
+      </c>
+      <c r="N1722" s="0" t="inlineStr">
+        <is>
+          <t>Emma Isom</t>
+        </is>
+      </c>
+      <c r="S1722" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1722" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1722" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1722" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="W1722" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1722" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1723">
+      <c r="A1723" s="0">
+        <v>1724</v>
+      </c>
+      <c r="B1723" s="0" t="inlineStr">
+        <is>
+          <t>Jen Jones</t>
+        </is>
+      </c>
+      <c r="C1723" s="0" t="inlineStr">
+        <is>
+          <t>Union Title</t>
+        </is>
+      </c>
+      <c r="K1723" s="0" t="inlineStr">
+        <is>
+          <t>8018992332</t>
+        </is>
+      </c>
+      <c r="M1723" s="0" t="inlineStr">
+        <is>
+          <t>jjones@uniontitle.net</t>
+        </is>
+      </c>
+      <c r="S1723" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1723" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U1723" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="V1723" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1723" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1723" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1724">
+      <c r="A1724" s="0">
+        <v>1725</v>
+      </c>
+      <c r="B1724" s="0" t="inlineStr">
+        <is>
+          <t>Jamie Fidler Cooke</t>
+        </is>
+      </c>
+      <c r="C1724" s="0" t="inlineStr">
+        <is>
+          <t>Intercap Lending</t>
+        </is>
+      </c>
+      <c r="K1724" s="0" t="inlineStr">
+        <is>
+          <t>8017031390</t>
+        </is>
+      </c>
+      <c r="M1724" s="0" t="inlineStr">
+        <is>
+          <t>jamiecooke@intercaplending.com</t>
+        </is>
+      </c>
+      <c r="S1724" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1724" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1724" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1724" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1724" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1724" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1725">
+      <c r="A1725" s="0">
+        <v>1726</v>
+      </c>
+      <c r="B1725" s="0" t="inlineStr">
+        <is>
+          <t>Emilie Demarco</t>
+        </is>
+      </c>
+      <c r="C1725" s="0" t="inlineStr">
+        <is>
+          <t>Cottonwood Title</t>
+        </is>
+      </c>
+      <c r="J1725" s="0" t="inlineStr">
+        <is>
+          <t>8016555260</t>
+        </is>
+      </c>
+      <c r="K1725" s="0" t="inlineStr">
+        <is>
+          <t>8013760844</t>
+        </is>
+      </c>
+      <c r="M1725" s="0" t="inlineStr">
+        <is>
+          <t>edemarco@cottonwoodtitle.com</t>
+        </is>
+      </c>
+      <c r="S1725" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1725" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U1725" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="V1725" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1725" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1725" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1726">
+      <c r="A1726" s="0">
+        <v>1727</v>
+      </c>
+      <c r="B1726" s="0" t="inlineStr">
+        <is>
+          <t>Kylie Sharp</t>
+        </is>
+      </c>
+      <c r="C1726" s="0" t="inlineStr">
+        <is>
+          <t>Novation Title</t>
+        </is>
+      </c>
+      <c r="J1726" s="0" t="inlineStr">
+        <is>
+          <t>8018278420</t>
+        </is>
+      </c>
+      <c r="M1726" s="0" t="inlineStr">
+        <is>
+          <t>kylieteam@novationtitle.com</t>
+        </is>
+      </c>
+      <c r="S1726" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1726" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U1726" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="V1726" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1726" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1726" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1727">
+      <c r="A1727" s="0">
+        <v>1728</v>
+      </c>
+      <c r="B1727" s="0" t="inlineStr">
+        <is>
+          <t>Robin Waner</t>
+        </is>
+      </c>
+      <c r="C1727" s="0" t="inlineStr">
+        <is>
+          <t>Keller Williams Westfield</t>
+        </is>
+      </c>
+      <c r="K1727" s="0" t="inlineStr">
+        <is>
+          <t>4806509032</t>
+        </is>
+      </c>
+      <c r="M1727" s="0" t="inlineStr">
+        <is>
+          <t>robinwarner1@gmail.com</t>
+        </is>
+      </c>
+      <c r="S1727" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1727" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1727" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1727" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="W1727" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1727" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1728">
+      <c r="A1728" s="0">
+        <v>1729</v>
+      </c>
+      <c r="B1728" s="0" t="inlineStr">
+        <is>
+          <t>Debbie Kraft</t>
+        </is>
+      </c>
+      <c r="C1728" s="0" t="inlineStr">
+        <is>
+          <t>Ease Mortgage</t>
+        </is>
+      </c>
+      <c r="K1728" s="0" t="inlineStr">
+        <is>
+          <t>8016161992</t>
+        </is>
+      </c>
+      <c r="M1728" s="0" t="inlineStr">
+        <is>
+          <t>debbie@kraftmortgageteam.com</t>
+        </is>
+      </c>
+      <c r="S1728" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1728" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1728" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1728" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1728" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1728" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1729">
+      <c r="A1729" s="0">
+        <v>1730</v>
+      </c>
+      <c r="B1729" s="0" t="inlineStr">
+        <is>
+          <t>Ryan Kramer</t>
+        </is>
+      </c>
+      <c r="C1729" s="0" t="inlineStr">
+        <is>
+          <t>REMAX Associates</t>
+        </is>
+      </c>
+      <c r="K1729" s="0" t="inlineStr">
+        <is>
+          <t>8019491803</t>
+        </is>
+      </c>
+      <c r="M1729" s="0" t="inlineStr">
+        <is>
+          <t>kramer@remaxofutah.com</t>
+        </is>
+      </c>
+      <c r="S1729" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1729" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1729" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1729" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="W1729" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1729" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1730">
+      <c r="A1730" s="0">
+        <v>1731</v>
+      </c>
+      <c r="B1730" s="0" t="inlineStr">
+        <is>
+          <t>Susan Piner</t>
+        </is>
+      </c>
+      <c r="C1730" s="0" t="inlineStr">
+        <is>
+          <t>Century 21</t>
+        </is>
+      </c>
+      <c r="K1730" s="0" t="inlineStr">
+        <is>
+          <t>8017357985</t>
+        </is>
+      </c>
+      <c r="M1730" s="0" t="inlineStr">
+        <is>
+          <t>susan@wasatchliferealty.com</t>
+        </is>
+      </c>
+      <c r="S1730" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1730" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1730" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1730" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="W1730" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1730" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1731">
+      <c r="A1731" s="0">
+        <v>1732</v>
+      </c>
+      <c r="B1731" s="0" t="inlineStr">
+        <is>
+          <t>Randall Hood</t>
+        </is>
+      </c>
+      <c r="C1731" s="0" t="inlineStr">
+        <is>
+          <t>Intercap Lending</t>
+        </is>
+      </c>
+      <c r="K1731" s="0" t="inlineStr">
+        <is>
+          <t>3858008360</t>
+        </is>
+      </c>
+      <c r="M1731" s="0" t="inlineStr">
+        <is>
+          <t>randall@intercaplending.com</t>
+        </is>
+      </c>
+      <c r="S1731" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1731" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1731" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1731" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1731" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1731" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1732">
+      <c r="A1732" s="0">
+        <v>1733</v>
+      </c>
+      <c r="B1732" s="0" t="inlineStr">
+        <is>
+          <t>Josh Kim</t>
+        </is>
+      </c>
+      <c r="C1732" s="0" t="inlineStr">
+        <is>
+          <t>Intercap Lending</t>
+        </is>
+      </c>
+      <c r="K1732" s="0" t="inlineStr">
+        <is>
+          <t>8018606014</t>
+        </is>
+      </c>
+      <c r="M1732" s="0" t="inlineStr">
+        <is>
+          <t>jkim@intercaplending.com</t>
+        </is>
+      </c>
+      <c r="S1732" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1732" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1732" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1732" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1732" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1732" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1733">
+      <c r="A1733" s="0">
+        <v>1734</v>
+      </c>
+      <c r="B1733" s="0" t="inlineStr">
+        <is>
+          <t>Trace Wilkinson</t>
+        </is>
+      </c>
+      <c r="C1733" s="0" t="inlineStr">
+        <is>
+          <t>Independent Home Loans</t>
+        </is>
+      </c>
+      <c r="K1733" s="0" t="inlineStr">
+        <is>
+          <t>8018644816</t>
+        </is>
+      </c>
+      <c r="M1733" s="0" t="inlineStr">
+        <is>
+          <t>trace@independenthomeloans.com</t>
+        </is>
+      </c>
+      <c r="S1733" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1733" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1733" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1733" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1733" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1733" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1734">
+      <c r="A1734" s="0">
+        <v>1735</v>
+      </c>
+      <c r="B1734" s="0" t="inlineStr">
+        <is>
+          <t>Shauna Jorgensen</t>
+        </is>
+      </c>
+      <c r="C1734" s="0" t="inlineStr">
+        <is>
+          <t>Realty Path</t>
+        </is>
+      </c>
+      <c r="K1734" s="0" t="inlineStr">
+        <is>
+          <t>8015186510</t>
+        </is>
+      </c>
+      <c r="M1734" s="0" t="inlineStr">
+        <is>
+          <t>shauna.jorgensen@gmail.com</t>
+        </is>
+      </c>
+      <c r="S1734" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1734" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1734" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1734" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="W1734" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1734" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1735">
+      <c r="A1735" s="0">
+        <v>1736</v>
+      </c>
+      <c r="B1735" s="0" t="inlineStr">
+        <is>
+          <t>Keia Blake</t>
+        </is>
+      </c>
+      <c r="C1735" s="0" t="inlineStr">
+        <is>
+          <t>Sun American Mortgage</t>
+        </is>
+      </c>
+      <c r="K1735" s="0" t="inlineStr">
+        <is>
+          <t>4356682485</t>
+        </is>
+      </c>
+      <c r="M1735" s="0" t="inlineStr">
+        <is>
+          <t>keia.blake@sunamerican.com</t>
+        </is>
+      </c>
+      <c r="S1735" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1735" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1735" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1735" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1735" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1735" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1736">
+      <c r="A1736" s="0">
+        <v>1737</v>
+      </c>
+      <c r="B1736" s="0" t="inlineStr">
+        <is>
+          <t>Leslie Heppler</t>
+        </is>
+      </c>
+      <c r="C1736" s="0" t="inlineStr">
+        <is>
+          <t>Eagle Gate Title</t>
+        </is>
+      </c>
+      <c r="J1736" s="0" t="inlineStr">
+        <is>
+          <t>4357036060</t>
+        </is>
+      </c>
+      <c r="M1736" s="0" t="inlineStr">
+        <is>
+          <t>stgteam@eaglegatetitle.com</t>
+        </is>
+      </c>
+      <c r="S1736" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1736" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U1736" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="V1736" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1736" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1736" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1737">
+      <c r="A1737" s="0">
+        <v>1738</v>
+      </c>
+      <c r="B1737" s="0" t="inlineStr">
+        <is>
+          <t>Samantha Gonzalez</t>
+        </is>
+      </c>
+      <c r="C1737" s="0" t="inlineStr">
+        <is>
+          <t>RealtyPath Advantage</t>
+        </is>
+      </c>
+      <c r="K1737" s="0" t="inlineStr">
+        <is>
+          <t>8014143578</t>
+        </is>
+      </c>
+      <c r="M1737" s="0" t="inlineStr">
+        <is>
+          <t>sammy@teamincome.net</t>
+        </is>
+      </c>
+      <c r="S1737" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1737" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1737" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1737" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="W1737" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1737" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1738">
+      <c r="A1738" s="0">
+        <v>1739</v>
+      </c>
+      <c r="B1738" s="0" t="inlineStr">
+        <is>
+          <t>Mitch Webb</t>
+        </is>
+      </c>
+      <c r="C1738" s="0" t="inlineStr">
+        <is>
+          <t>Direct Rate</t>
+        </is>
+      </c>
+      <c r="K1738" s="0" t="inlineStr">
+        <is>
+          <t>8015062700</t>
+        </is>
+      </c>
+      <c r="M1738" s="0" t="inlineStr">
+        <is>
+          <t>mitch@directrate.com</t>
+        </is>
+      </c>
+      <c r="S1738" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1738" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1738" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1738" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1738" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1738" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1739">
+      <c r="A1739" s="0">
+        <v>1740</v>
+      </c>
+      <c r="B1739" s="0" t="inlineStr">
+        <is>
+          <t>Sid Spilseth</t>
+        </is>
+      </c>
+      <c r="C1739" s="0" t="inlineStr">
+        <is>
+          <t>Deseret First Credit Union</t>
+        </is>
+      </c>
+      <c r="K1739" s="0" t="inlineStr">
+        <is>
+          <t>4352150987</t>
+        </is>
+      </c>
+      <c r="M1739" s="0" t="inlineStr">
+        <is>
+          <t>Sid.spilseth@dfcu.com</t>
+        </is>
+      </c>
+      <c r="S1739" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1739" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1739" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1739" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1739" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1739" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1740">
+      <c r="A1740" s="0">
+        <v>1741</v>
+      </c>
+      <c r="B1740" s="0" t="inlineStr">
+        <is>
+          <t>Kristy Imhof</t>
+        </is>
+      </c>
+      <c r="C1740" s="0" t="inlineStr">
+        <is>
+          <t>High Road Properties</t>
+        </is>
+      </c>
+      <c r="K1740" s="0" t="inlineStr">
+        <is>
+          <t>8016318854</t>
+        </is>
+      </c>
+      <c r="M1740" s="0" t="inlineStr">
+        <is>
+          <t>kristy@highroadutah.com</t>
+        </is>
+      </c>
+      <c r="S1740" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1740" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1740" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1740" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="W1740" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1740" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1741">
+      <c r="A1741" s="0">
+        <v>1742</v>
+      </c>
+      <c r="B1741" s="0" t="inlineStr">
+        <is>
+          <t>Raelene Christopherson</t>
+        </is>
+      </c>
+      <c r="C1741" s="0" t="inlineStr">
+        <is>
+          <t>CFI Realty</t>
+        </is>
+      </c>
+      <c r="J1741" s="0" t="inlineStr">
+        <is>
+          <t>8013807144</t>
+        </is>
+      </c>
+      <c r="M1741" s="0" t="inlineStr">
+        <is>
+          <t>raelene@cfirealty.com</t>
+        </is>
+      </c>
+      <c r="S1741" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1741" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1741" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1741" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="W1741" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1741" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1742">
+      <c r="A1742" s="0">
+        <v>1743</v>
+      </c>
+      <c r="B1742" s="0" t="inlineStr">
+        <is>
+          <t>Shayna Clark</t>
+        </is>
+      </c>
+      <c r="C1742" s="0" t="inlineStr">
+        <is>
+          <t>Iconic Realty Network</t>
+        </is>
+      </c>
+      <c r="K1742" s="0" t="inlineStr">
+        <is>
+          <t>4358408845</t>
+        </is>
+      </c>
+      <c r="M1742" s="0" t="inlineStr">
+        <is>
+          <t>shaynaclarkrealestate@gmail.com</t>
+        </is>
+      </c>
+      <c r="S1742" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1742" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1742" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1742" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1742" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1742" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1743">
+      <c r="A1743" s="0">
+        <v>1744</v>
+      </c>
+      <c r="B1743" s="0" t="inlineStr">
+        <is>
+          <t>Greg Goold</t>
+        </is>
+      </c>
+      <c r="C1743" s="0" t="inlineStr">
+        <is>
+          <t>Mountain Point Mortgage</t>
+        </is>
+      </c>
+      <c r="K1743" s="0" t="inlineStr">
+        <is>
+          <t>4357033800</t>
+        </is>
+      </c>
+      <c r="M1743" s="0" t="inlineStr">
+        <is>
+          <t>greg@mountainpoint.mortgage</t>
+        </is>
+      </c>
+      <c r="S1743" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1743" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1743" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1743" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1743" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1743" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1744">
+      <c r="A1744" s="0">
+        <v>1745</v>
+      </c>
+      <c r="B1744" s="0" t="inlineStr">
+        <is>
+          <t>Jeremiah Carlson</t>
+        </is>
+      </c>
+      <c r="C1744" s="0" t="inlineStr">
+        <is>
+          <t>Cyprus Credit Union</t>
+        </is>
+      </c>
+      <c r="K1744" s="0" t="inlineStr">
+        <is>
+          <t>8017593067</t>
+        </is>
+      </c>
+      <c r="M1744" s="0" t="inlineStr">
+        <is>
+          <t>jermiah.carlson@cypruscu.com</t>
+        </is>
+      </c>
+      <c r="S1744" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1744" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1744" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1744" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1744" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1744" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1745">
+      <c r="A1745" s="0">
+        <v>1746</v>
+      </c>
+      <c r="B1745" s="0" t="inlineStr">
+        <is>
+          <t>Jared Browning</t>
+        </is>
+      </c>
+      <c r="C1745" s="0" t="inlineStr">
+        <is>
+          <t>Sympli Mortgage</t>
+        </is>
+      </c>
+      <c r="K1745" s="0" t="inlineStr">
+        <is>
+          <t>8018426206</t>
+        </is>
+      </c>
+      <c r="M1745" s="0" t="inlineStr">
+        <is>
+          <t>jared@symplimortgage.com</t>
+        </is>
+      </c>
+      <c r="S1745" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1745" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1745" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1745" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1745" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1745" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1746">
+      <c r="A1746" s="0">
+        <v>1747</v>
+      </c>
+      <c r="B1746" s="0" t="inlineStr">
+        <is>
+          <t>Kaitlyn Petersen</t>
+        </is>
+      </c>
+      <c r="C1746" s="0" t="inlineStr">
+        <is>
+          <t>EXP Realty</t>
+        </is>
+      </c>
+      <c r="K1746" s="0" t="inlineStr">
+        <is>
+          <t>3858326377</t>
+        </is>
+      </c>
+      <c r="M1746" s="0" t="inlineStr">
+        <is>
+          <t>kpetersen@liveutah.com</t>
+        </is>
+      </c>
+      <c r="S1746" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1746" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1746" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1746" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1746" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1746" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1747">
+      <c r="A1747" s="0">
+        <v>1748</v>
+      </c>
+      <c r="B1747" s="0" t="inlineStr">
+        <is>
+          <t>Kelsey Mount</t>
+        </is>
+      </c>
+      <c r="C1747" s="0" t="inlineStr">
+        <is>
+          <t>Old Republic Title</t>
+        </is>
+      </c>
+      <c r="K1747" s="0" t="inlineStr">
+        <is>
+          <t>8012173127</t>
+        </is>
+      </c>
+      <c r="M1747" s="0" t="inlineStr">
+        <is>
+          <t>kmount1@oldrepublictitle.com</t>
+        </is>
+      </c>
+      <c r="S1747" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1747" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U1747" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1747" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1747" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1747" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1748">
+      <c r="A1748" s="0">
+        <v>1749</v>
+      </c>
+      <c r="B1748" s="0" t="inlineStr">
+        <is>
+          <t>Spencer Romney</t>
+        </is>
+      </c>
+      <c r="K1748" s="0" t="inlineStr">
+        <is>
+          <t>8018709119</t>
+        </is>
+      </c>
+      <c r="M1748" s="0" t="inlineStr">
+        <is>
+          <t>spencer@romneyteam.com</t>
+        </is>
+      </c>
+      <c r="S1748" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1748" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1748" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1748" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1748" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1748" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1749">
+      <c r="A1749" s="0">
+        <v>1750</v>
+      </c>
+      <c r="B1749" s="0" t="inlineStr">
+        <is>
+          <t>Troy Norris</t>
+        </is>
+      </c>
+      <c r="C1749" s="0" t="inlineStr">
+        <is>
+          <t>City Creek Mortgage</t>
+        </is>
+      </c>
+      <c r="K1749" s="0" t="inlineStr">
+        <is>
+          <t>8017843702</t>
+        </is>
+      </c>
+      <c r="M1749" s="0" t="inlineStr">
+        <is>
+          <t>troy@citycreekmortgage.com</t>
+        </is>
+      </c>
+      <c r="S1749" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1749" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1749" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1749" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1749" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1749" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1750">
+      <c r="A1750" s="0">
+        <v>1751</v>
+      </c>
+      <c r="B1750" s="0" t="inlineStr">
+        <is>
+          <t>Jose Ornelas</t>
+        </is>
+      </c>
+      <c r="C1750" s="0" t="inlineStr">
+        <is>
+          <t>First American Title</t>
+        </is>
+      </c>
+      <c r="K1750" s="0" t="inlineStr">
+        <is>
+          <t>8018510810</t>
+        </is>
+      </c>
+      <c r="M1750" s="0" t="inlineStr">
+        <is>
+          <t>jornelas@firstam.com</t>
+        </is>
+      </c>
+      <c r="S1750" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1750" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U1750" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1750" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1750" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1750" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1751">
+      <c r="A1751" s="0">
+        <v>1752</v>
+      </c>
+      <c r="B1751" s="0" t="inlineStr">
+        <is>
+          <t>McKay Garrett</t>
+        </is>
+      </c>
+      <c r="C1751" s="0" t="inlineStr">
+        <is>
+          <t>Lancaster &amp; Co.</t>
+        </is>
+      </c>
+      <c r="K1751" s="0" t="inlineStr">
+        <is>
+          <t>8018502233</t>
+        </is>
+      </c>
+      <c r="M1751" s="0" t="inlineStr">
+        <is>
+          <t>mckay@steadywayhome.com</t>
+        </is>
+      </c>
+      <c r="S1751" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1751" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1751" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1751" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1751" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1751" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1752">
+      <c r="A1752" s="0">
+        <v>1753</v>
+      </c>
+      <c r="B1752" s="0" t="inlineStr">
+        <is>
+          <t>Janet Lunt</t>
+        </is>
+      </c>
+      <c r="C1752" s="0" t="inlineStr">
+        <is>
+          <t>Prospect Title</t>
+        </is>
+      </c>
+      <c r="J1752" s="0" t="inlineStr">
+        <is>
+          <t>8012251924</t>
+        </is>
+      </c>
+      <c r="M1752" s="0" t="inlineStr">
+        <is>
+          <t>janet@prospectut.com</t>
+        </is>
+      </c>
+      <c r="N1752" s="0" t="inlineStr">
+        <is>
+          <t>Lauren</t>
+        </is>
+      </c>
+      <c r="R1752" s="0" t="inlineStr">
+        <is>
+          <t>lauren@prospectut.com</t>
+        </is>
+      </c>
+      <c r="S1752" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1752" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1752" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="V1752" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1752" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1752" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1753">
+      <c r="A1753" s="0">
+        <v>1754</v>
+      </c>
+      <c r="B1753" s="0" t="inlineStr">
+        <is>
+          <t>Lori Summers</t>
+        </is>
+      </c>
+      <c r="C1753" s="0" t="inlineStr">
+        <is>
+          <t>Seasons Real Estate</t>
+        </is>
+      </c>
+      <c r="K1753" s="0" t="inlineStr">
+        <is>
+          <t>8017877564</t>
+        </is>
+      </c>
+      <c r="M1753" s="0" t="inlineStr">
+        <is>
+          <t>lorisummersrealtor@gmail.com</t>
+        </is>
+      </c>
+      <c r="R1753" s="0" t="inlineStr">
+        <is>
+          <t>admin@utseasons.com</t>
+        </is>
+      </c>
+      <c r="S1753" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1753" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1753" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1753" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="W1753" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="X1753" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1754">
+      <c r="A1754" s="0">
+        <v>1755</v>
+      </c>
+      <c r="B1754" s="0" t="inlineStr">
+        <is>
+          <t>Kristopher Matyas</t>
+        </is>
+      </c>
+      <c r="C1754" s="0" t="inlineStr">
+        <is>
+          <t>Barrett Financial</t>
+        </is>
+      </c>
+      <c r="K1754" s="0" t="inlineStr">
+        <is>
+          <t>8016380507</t>
+        </is>
+      </c>
+      <c r="M1754" s="0" t="inlineStr">
+        <is>
+          <t>Kristopher@barrettfinancial.com</t>
+        </is>
+      </c>
+      <c r="N1754" s="0" t="inlineStr">
+        <is>
+          <t>Mia</t>
+        </is>
+      </c>
+      <c r="O1754" s="0" t="inlineStr">
+        <is>
+          <t>8018727459</t>
+        </is>
+      </c>
+      <c r="S1754" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T1754" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1754" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1754" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1754" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1754" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1755">
+      <c r="A1755" s="0">
+        <v>1756</v>
+      </c>
+      <c r="B1755" s="0" t="inlineStr">
+        <is>
+          <t>Ryan Hoskins</t>
+        </is>
+      </c>
+      <c r="C1755" s="0" t="inlineStr">
+        <is>
+          <t>Fidelity National Title</t>
+        </is>
+      </c>
+      <c r="J1755" s="0" t="inlineStr">
+        <is>
+          <t>8015457919</t>
+        </is>
+      </c>
+      <c r="K1755" s="0" t="inlineStr">
+        <is>
+          <t>8012321729</t>
+        </is>
+      </c>
+      <c r="M1755" s="0" t="inlineStr">
+        <is>
+          <t>Ut.TeamRyan@fnf.com</t>
+        </is>
+      </c>
+      <c r="S1755" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1755" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="U1755" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V1755" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1755" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1755" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1756">
+      <c r="A1756" s="0">
+        <v>1757</v>
+      </c>
+      <c r="B1756" s="0" t="inlineStr">
+        <is>
+          <t>Dave Wright</t>
+        </is>
+      </c>
+      <c r="C1756" s="0" t="inlineStr">
+        <is>
+          <t>Fidelity National Title</t>
+        </is>
+      </c>
+      <c r="J1756" s="0" t="inlineStr">
+        <is>
+          <t>8019929666</t>
+        </is>
+      </c>
+      <c r="K1756" s="0" t="inlineStr">
+        <is>
+          <t>8019159494</t>
+        </is>
+      </c>
+      <c r="M1756" s="0" t="inlineStr">
+        <is>
+          <t>Ut.TeamDave@fnf.com</t>
+        </is>
+      </c>
+      <c r="S1756" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T1756" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U1756" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="V1756" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W1756" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X1756" s="0" t="b">
         <v>0</v>
       </c>
     </row>
